--- a/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0003T0006Z000C1N9_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0003T0006Z000C1N9_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.015405824637347</v>
+        <v>1.140003446503569</v>
       </c>
       <c r="D2" t="n">
-        <v>7.133366181603046</v>
+        <v>1.159172004510495</v>
       </c>
       <c r="E2" t="n">
-        <v>46.73156112102974</v>
+        <v>7.593878682167333</v>
       </c>
       <c r="F2" t="n">
-        <v>46.71042493279224</v>
+        <v>7.59044405157874</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>12.45080783573912</v>
+        <v>2.023256273307607</v>
       </c>
       <c r="D3" t="n">
-        <v>12.36057011503284</v>
+        <v>2.008592643692837</v>
       </c>
       <c r="E3" t="n">
-        <v>46.73156112102974</v>
+        <v>7.593878682167333</v>
       </c>
       <c r="F3" t="n">
-        <v>46.71042493279224</v>
+        <v>7.59044405157874</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>1.249768489369445</v>
+        <v>0.2030873795225348</v>
       </c>
       <c r="D4" t="n">
-        <v>1.12930813038872</v>
+        <v>0.183512571188167</v>
       </c>
       <c r="E4" t="n">
-        <v>46.73156112102974</v>
+        <v>7.593878682167333</v>
       </c>
       <c r="F4" t="n">
-        <v>46.71042493279224</v>
+        <v>7.59044405157874</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>124.1472857024395</v>
+        <v>20.17393392664642</v>
       </c>
       <c r="D5" t="n">
-        <v>124.0610800361963</v>
+        <v>20.1599255058819</v>
       </c>
       <c r="E5" t="n">
-        <v>46.73156112102974</v>
+        <v>7.593878682167333</v>
       </c>
       <c r="F5" t="n">
-        <v>46.71042493279224</v>
+        <v>7.59044405157874</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>23.0564231395089</v>
+        <v>3.746668760170197</v>
       </c>
       <c r="D6" t="n">
-        <v>22.96734944923151</v>
+        <v>3.73219428550012</v>
       </c>
       <c r="E6" t="n">
-        <v>46.73156112102974</v>
+        <v>7.593878682167333</v>
       </c>
       <c r="F6" t="n">
-        <v>46.71042493279224</v>
+        <v>7.59044405157874</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>67.83292930685238</v>
+        <v>11.02285101236351</v>
       </c>
       <c r="D7" t="n">
-        <v>67.73095793668196</v>
+        <v>11.00628066471082</v>
       </c>
       <c r="E7" t="n">
-        <v>46.73156112102974</v>
+        <v>7.593878682167333</v>
       </c>
       <c r="F7" t="n">
-        <v>46.71042493279224</v>
+        <v>7.59044405157874</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>50.38269949004521</v>
+        <v>8.187188667132347</v>
       </c>
       <c r="D8" t="n">
-        <v>50.26504103914143</v>
+        <v>8.168069168860482</v>
       </c>
       <c r="E8" t="n">
-        <v>46.73156112102974</v>
+        <v>7.593878682167333</v>
       </c>
       <c r="F8" t="n">
-        <v>46.71042493279224</v>
+        <v>7.59044405157874</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>97.13741777897695</v>
+        <v>15.78483038908375</v>
       </c>
       <c r="D9" t="n">
-        <v>97.03467131050846</v>
+        <v>15.76813408795763</v>
       </c>
       <c r="E9" t="n">
-        <v>46.73156112102974</v>
+        <v>7.593878682167333</v>
       </c>
       <c r="F9" t="n">
-        <v>46.71042493279224</v>
+        <v>7.59044405157874</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>51.01328941887103</v>
+        <v>8.289659530566544</v>
       </c>
       <c r="D10" t="n">
-        <v>50.89880317957741</v>
+        <v>8.271055516681329</v>
       </c>
       <c r="E10" t="n">
-        <v>46.73156112102974</v>
+        <v>7.593878682167333</v>
       </c>
       <c r="F10" t="n">
-        <v>46.71042493279224</v>
+        <v>7.59044405157874</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>65.52563981960454</v>
+        <v>10.64791647068574</v>
       </c>
       <c r="D11" t="n">
-        <v>65.41391937531482</v>
+        <v>10.62976189848866</v>
       </c>
       <c r="E11" t="n">
-        <v>46.73156112102974</v>
+        <v>7.593878682167333</v>
       </c>
       <c r="F11" t="n">
-        <v>46.71042493279224</v>
+        <v>7.59044405157874</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>81.06868774304181</v>
+        <v>13.17366175824429</v>
       </c>
       <c r="D12" t="n">
-        <v>80.94797306897281</v>
+        <v>13.15404562370808</v>
       </c>
       <c r="E12" t="n">
-        <v>46.73156112102974</v>
+        <v>7.593878682167333</v>
       </c>
       <c r="F12" t="n">
-        <v>46.71042493279224</v>
+        <v>7.59044405157874</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>132.4789031244121</v>
+        <v>21.52782175771696</v>
       </c>
       <c r="D13" t="n">
-        <v>132.3654672504993</v>
+        <v>21.50938842820613</v>
       </c>
       <c r="E13" t="n">
-        <v>46.73156112102974</v>
+        <v>7.593878682167333</v>
       </c>
       <c r="F13" t="n">
-        <v>46.71042493279224</v>
+        <v>7.59044405157874</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>99.89720904044647</v>
+        <v>16.23329646907255</v>
       </c>
       <c r="D14" t="n">
-        <v>99.77762446548398</v>
+        <v>16.21386397564115</v>
       </c>
       <c r="E14" t="n">
-        <v>46.73156112102974</v>
+        <v>7.593878682167333</v>
       </c>
       <c r="F14" t="n">
-        <v>46.71042493279224</v>
+        <v>7.59044405157874</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>118.8035296531992</v>
+        <v>19.30557356864486</v>
       </c>
       <c r="D15" t="n">
-        <v>118.6832788788655</v>
+        <v>19.28603281781565</v>
       </c>
       <c r="E15" t="n">
-        <v>46.73156112102974</v>
+        <v>7.593878682167333</v>
       </c>
       <c r="F15" t="n">
-        <v>46.71042493279224</v>
+        <v>7.59044405157874</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>135.5444086432684</v>
+        <v>22.02596640453112</v>
       </c>
       <c r="D16" t="n">
-        <v>135.4264761467865</v>
+        <v>22.0068023738528</v>
       </c>
       <c r="E16" t="n">
-        <v>46.73156112102974</v>
+        <v>7.593878682167333</v>
       </c>
       <c r="F16" t="n">
-        <v>46.71042493279224</v>
+        <v>7.59044405157874</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>106.0049429678279</v>
+        <v>17.22580323227204</v>
       </c>
       <c r="D17" t="n">
-        <v>105.8852132434425</v>
+        <v>17.20634715205941</v>
       </c>
       <c r="E17" t="n">
-        <v>46.73156112102974</v>
+        <v>7.593878682167333</v>
       </c>
       <c r="F17" t="n">
-        <v>46.71042493279224</v>
+        <v>7.59044405157874</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>103.294964142852</v>
+        <v>16.78543167321345</v>
       </c>
       <c r="D18" t="n">
-        <v>103.177350740188</v>
+        <v>16.76631949528054</v>
       </c>
       <c r="E18" t="n">
-        <v>46.73156112102974</v>
+        <v>7.593878682167333</v>
       </c>
       <c r="F18" t="n">
-        <v>46.71042493279224</v>
+        <v>7.59044405157874</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>115.4699795049419</v>
+        <v>18.76387166955307</v>
       </c>
       <c r="D19" t="n">
-        <v>115.3501037144966</v>
+        <v>18.74439185360569</v>
       </c>
       <c r="E19" t="n">
-        <v>46.73156112102974</v>
+        <v>7.593878682167333</v>
       </c>
       <c r="F19" t="n">
-        <v>46.71042493279224</v>
+        <v>7.59044405157874</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>121.5658049331666</v>
+        <v>19.75444330163957</v>
       </c>
       <c r="D20" t="n">
-        <v>121.4450690280815</v>
+        <v>19.73482371706325</v>
       </c>
       <c r="E20" t="n">
-        <v>46.73156112102974</v>
+        <v>7.593878682167333</v>
       </c>
       <c r="F20" t="n">
-        <v>46.71042493279224</v>
+        <v>7.59044405157874</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>146.9335718246727</v>
+        <v>23.87670542150932</v>
       </c>
       <c r="D21" t="n">
-        <v>146.8130176409885</v>
+        <v>23.85711536666063</v>
       </c>
       <c r="E21" t="n">
-        <v>46.73156112102974</v>
+        <v>7.593878682167333</v>
       </c>
       <c r="F21" t="n">
-        <v>46.71042493279224</v>
+        <v>7.59044405157874</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>138.2931522350447</v>
+        <v>22.47263723819476</v>
       </c>
       <c r="D22" t="n">
-        <v>138.1723902811865</v>
+        <v>22.4530134206928</v>
       </c>
       <c r="E22" t="n">
-        <v>46.73156112102974</v>
+        <v>7.593878682167333</v>
       </c>
       <c r="F22" t="n">
-        <v>46.71042493279224</v>
+        <v>7.59044405157874</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>126.0885457439549</v>
+        <v>20.48938868339268</v>
       </c>
       <c r="D23" t="n">
-        <v>125.9698903533228</v>
+        <v>20.47010718241496</v>
       </c>
       <c r="E23" t="n">
-        <v>46.73156112102974</v>
+        <v>7.593878682167333</v>
       </c>
       <c r="F23" t="n">
-        <v>46.71042493279224</v>
+        <v>7.59044405157874</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>130.6153466824438</v>
+        <v>21.22499383589712</v>
       </c>
       <c r="D24" t="n">
-        <v>130.504544490194</v>
+        <v>21.20698847965653</v>
       </c>
       <c r="E24" t="n">
-        <v>46.73156112102974</v>
+        <v>7.593878682167333</v>
       </c>
       <c r="F24" t="n">
-        <v>46.71042493279224</v>
+        <v>7.59044405157874</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>141.4327179381624</v>
+        <v>22.98281666495139</v>
       </c>
       <c r="D25" t="n">
-        <v>141.316851057316</v>
+        <v>22.96398829681385</v>
       </c>
       <c r="E25" t="n">
-        <v>46.73156112102974</v>
+        <v>7.593878682167333</v>
       </c>
       <c r="F25" t="n">
-        <v>46.71042493279224</v>
+        <v>7.59044405157874</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>169.7075556812541</v>
+        <v>27.5774777982038</v>
       </c>
       <c r="D26" t="n">
-        <v>169.5868719426803</v>
+        <v>27.55786669068556</v>
       </c>
       <c r="E26" t="n">
-        <v>46.73156112102974</v>
+        <v>7.593878682167333</v>
       </c>
       <c r="F26" t="n">
-        <v>46.71042493279224</v>
+        <v>7.59044405157874</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
